--- a/education_forms/036_finance_mba_admission_form--education_forms.xlsx
+++ b/education_forms/036_finance_mba_admission_form--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>comments_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Comments 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>assigned_tool_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Assigned Tool</t>
+          <t>Assigned Tool 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>submitted_by</t>
+          <t>submitted_by_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Submitted By</t>
+          <t>Submitted By 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>submitted_date</t>
+          <t>submitted_date_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Submitted Date</t>
+          <t>Submitted Date 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>submitted_time</t>
+          <t>submitted_time_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Submitted Time</t>
+          <t>Submitted Time 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_"master's"}</t>
+          <t>master's</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': "Master's"}</t>
+          <t>Master's</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_"bachelor's"}</t>
+          <t>bachelor's</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': "Bachelor's"}</t>
+          <t>Bachelor's</t>
         </is>
       </c>
     </row>
